--- a/outputs/marine_equipment/Отгрузки_факт.xlsx
+++ b/outputs/marine_equipment/Отгрузки_факт.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>Б/у</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
